--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B0AAC0-345C-4CCD-A57A-3E93B13416B3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -143,10 +143,10 @@
     <t>A A</t>
   </si>
   <si>
-    <t xml:space="preserve">B B </t>
-  </si>
-  <si>
     <t>C C</t>
+  </si>
+  <si>
+    <t>B B</t>
   </si>
 </sst>
 </file>
@@ -785,10 +785,10 @@
     </row>
     <row r="18" spans="7:13" x14ac:dyDescent="0.25">
       <c r="H18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -801,10 +801,10 @@
     </row>
     <row r="19" spans="7:13" x14ac:dyDescent="0.25">
       <c r="H19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -989,8 +989,8 @@
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I19:K19"/>
     <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I19:K19"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B0AAC0-345C-4CCD-A57A-3E93B13416B3}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6363B6A6-75BD-4727-AE81-134ED8895B9D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="101">
   <si>
     <t>A</t>
   </si>
@@ -56,9 +56,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>Cards</t>
-  </si>
-  <si>
     <t>Suits</t>
   </si>
   <si>
@@ -147,6 +144,204 @@
   </si>
   <si>
     <t>B B</t>
+  </si>
+  <si>
+    <t>default cards</t>
+  </si>
+  <si>
+    <t>target features:</t>
+  </si>
+  <si>
+    <t>destroy emotions for bonus vp</t>
+  </si>
+  <si>
+    <t>for cards with certain suit count</t>
+  </si>
+  <si>
+    <t>for cards on count down</t>
+  </si>
+  <si>
+    <t>for in hand</t>
+  </si>
+  <si>
+    <t>TODO: card buffing mb idk</t>
+  </si>
+  <si>
+    <t>bonus A for hand</t>
+  </si>
+  <si>
+    <t>A B in hand</t>
+  </si>
+  <si>
+    <t>B C in hand</t>
+  </si>
+  <si>
+    <t>C E in hand</t>
+  </si>
+  <si>
+    <t>D E in hand</t>
+  </si>
+  <si>
+    <t>E A in hand</t>
+  </si>
+  <si>
+    <t>A B C in hand</t>
+  </si>
+  <si>
+    <t>B C D in hand</t>
+  </si>
+  <si>
+    <t>C D E in hand</t>
+  </si>
+  <si>
+    <t>D E A in hand</t>
+  </si>
+  <si>
+    <t>E A B in hand</t>
+  </si>
+  <si>
+    <t>A PLACED</t>
+  </si>
+  <si>
+    <t>B PLACED</t>
+  </si>
+  <si>
+    <t>C PLACED</t>
+  </si>
+  <si>
+    <t>D PLACED</t>
+  </si>
+  <si>
+    <t>E PLACED</t>
+  </si>
+  <si>
+    <t>A A PLACED</t>
+  </si>
+  <si>
+    <t>E E E E</t>
+  </si>
+  <si>
+    <t>B B PLACED</t>
+  </si>
+  <si>
+    <t>C C PLACED</t>
+  </si>
+  <si>
+    <t>D D PLACED</t>
+  </si>
+  <si>
+    <t>E E PLACED</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>bonus C for hand</t>
+  </si>
+  <si>
+    <t>B B B B</t>
+  </si>
+  <si>
+    <t>FOR EACH CARD ON COUNTDOWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E </t>
+  </si>
+  <si>
+    <t>BONUS D FOR SCERTAIN SUIT COUNT</t>
+  </si>
+  <si>
+    <t>CARD W 1 SUIT IS PLACED</t>
+  </si>
+  <si>
+    <t>CARD W 2 SUITS IS PLACED</t>
+  </si>
+  <si>
+    <t>CARD W 3 SUITS IS PLACED</t>
+  </si>
+  <si>
+    <t>CARD W 4 SUITS IS PLACED</t>
+  </si>
+  <si>
+    <t>FOR EACH 2 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>FOR EACH 1 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>FOR EACH 3 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>C C C C</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>BONUS E FOR DESTROYING</t>
+  </si>
+  <si>
+    <t>DESTOYS 2 A</t>
+  </si>
+  <si>
+    <t>DESTOYS 2 B</t>
+  </si>
+  <si>
+    <t>DESTOYS 2 C</t>
+  </si>
+  <si>
+    <t>DESTOYS 2 D</t>
+  </si>
+  <si>
+    <t>DESTOYS 2 E</t>
+  </si>
+  <si>
+    <t>DESTOYS 3 A</t>
+  </si>
+  <si>
+    <t>DESTOYS 3 B</t>
+  </si>
+  <si>
+    <t>DESTOYS 3 C</t>
+  </si>
+  <si>
+    <t>DESTOYS 3 D</t>
+  </si>
+  <si>
+    <t>DESTOYS 3 E</t>
+  </si>
+  <si>
+    <t>DESTOYS 4 A</t>
+  </si>
+  <si>
+    <t>DESTOYS 4 B</t>
+  </si>
+  <si>
+    <t>DESTOYS 4 C</t>
+  </si>
+  <si>
+    <t>DESTOYS 4 D</t>
+  </si>
+  <si>
+    <t>DESTOYS 4  E</t>
+  </si>
+  <si>
+    <t>D D D D</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>bonus B RNDOM SHIT?</t>
   </si>
 </sst>
 </file>
@@ -524,13 +719,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC38A9E3-0959-4F47-9569-6C1D59F951C2}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,41 +742,67 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="H3" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="H5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -590,13 +812,22 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>2</v>
+      </c>
       <c r="H6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -606,13 +837,29 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="2"/>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>3</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -622,13 +869,50 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="2"/>
+      <c r="X7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="2"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>4</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -638,13 +922,74 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X8">
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="2">
+        <v>150</v>
+      </c>
+      <c r="AE8" s="2"/>
+      <c r="AG8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+      <c r="AM8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>5</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -654,13 +999,65 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="2">
+        <v>125</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+      <c r="AM9" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN9" s="2"/>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>6</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -670,13 +1067,44 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q10" s="2"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AE10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG10">
+        <v>2</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN10" s="2"/>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>7</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -686,13 +1114,65 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="2">
+        <v>125</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>3</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="1"/>
+      <c r="AM11" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN11" s="2"/>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>8</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -702,13 +1182,44 @@
       <c r="M12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q12" s="2"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AE12" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG12">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN12" s="2"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>9</v>
+      </c>
       <c r="H13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -718,13 +1229,65 @@
       <c r="M13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="2">
+        <v>125</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG13">
+        <v>5</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN13" s="2"/>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>10</v>
+      </c>
       <c r="H14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -734,13 +1297,44 @@
       <c r="M14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q14" s="2"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AE14" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG14">
+        <v>6</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN14" s="2"/>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>11</v>
+      </c>
       <c r="H15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -750,13 +1344,65 @@
       <c r="M15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O15">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="2">
+        <v>125</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>7</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15">
+        <v>75</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG15">
+        <v>7</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN15" s="2"/>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>12</v>
+      </c>
       <c r="H16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -766,13 +1412,44 @@
       <c r="M16" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AE16" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG16">
+        <v>8</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN16" s="2"/>
+    </row>
+    <row r="17" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>13</v>
+      </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -782,13 +1459,65 @@
       <c r="M17" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="2">
+        <v>125</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17">
+        <v>75</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG17">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN17" s="2"/>
+    </row>
+    <row r="18" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>14</v>
+      </c>
       <c r="H18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -798,13 +1527,44 @@
       <c r="M18" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AE18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN18" s="2"/>
+    </row>
+    <row r="19" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>15</v>
+      </c>
       <c r="H19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -814,13 +1574,65 @@
       <c r="M19" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O19">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="2">
+        <v>250</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19">
+        <v>175</v>
+      </c>
+      <c r="AE19" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG19">
+        <v>11</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN19" s="2"/>
+    </row>
+    <row r="20" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>16</v>
+      </c>
       <c r="G20">
         <v>2</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -831,13 +1643,65 @@
       <c r="M20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O20">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="2">
+        <v>250</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20">
+        <v>175</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG20">
+        <v>12</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN20" s="2"/>
+    </row>
+    <row r="21" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>17</v>
+      </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -848,13 +1712,65 @@
       <c r="M21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="2">
+        <v>250</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21">
+        <v>175</v>
+      </c>
+      <c r="AE21" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG21">
+        <v>13</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+      <c r="AM21" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN21" s="2"/>
+    </row>
+    <row r="22" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>18</v>
+      </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -865,13 +1781,65 @@
       <c r="M22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O22">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="2">
+        <v>250</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>12</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22">
+        <v>175</v>
+      </c>
+      <c r="AE22" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG22">
+        <v>14</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
+      <c r="AM22" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN22" s="2"/>
+    </row>
+    <row r="23" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>19</v>
+      </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -882,13 +1850,65 @@
       <c r="M23" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="2">
+        <v>250</v>
+      </c>
+      <c r="V23" s="2">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>13</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23">
+        <v>175</v>
+      </c>
+      <c r="AE23" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG23">
+        <v>15</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
+      <c r="AM23" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN23" s="2"/>
+    </row>
+    <row r="24" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>20</v>
+      </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -899,8 +1919,49 @@
       <c r="M24" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O24">
+        <v>11</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="2">
+        <v>50</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>14</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="2">
+        <v>50</v>
+      </c>
+      <c r="AE24" s="2"/>
+      <c r="AG24">
+        <v>16</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM24" s="2">
+        <v>50</v>
+      </c>
+      <c r="AN24" s="2"/>
+    </row>
+    <row r="25" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -911,8 +1972,25 @@
       <c r="M25" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O25">
+        <v>12</v>
+      </c>
+      <c r="P25" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AE25" s="2"/>
+    </row>
+    <row r="26" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -923,8 +2001,33 @@
       <c r="M26" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O26">
+        <v>13</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26">
+        <v>175</v>
+      </c>
+      <c r="V26" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AE26" s="2"/>
+    </row>
+    <row r="27" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -935,8 +2038,28 @@
       <c r="M27" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="O27">
+        <v>14</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27">
+        <v>75</v>
+      </c>
+      <c r="V27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -947,8 +2070,13 @@
       <c r="M28" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="Q28" s="2"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="V28" s="2"/>
+    </row>
+    <row r="29" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H29" s="2"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -959,8 +2087,22 @@
       <c r="M29" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="Q29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="2"/>
+      <c r="Z29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="2"/>
+    </row>
+    <row r="30" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -971,14 +2113,721 @@
       <c r="M30" s="2">
         <v>0</v>
       </c>
+      <c r="O30" t="s">
+        <v>64</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" t="s">
+        <v>8</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>21</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="2">
+        <v>50</v>
+      </c>
+      <c r="M31" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="2">
+        <v>100</v>
+      </c>
+      <c r="AE31" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="6:40" x14ac:dyDescent="0.25">
+      <c r="H32" s="2"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="M32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="X32">
+        <v>2</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="2">
+        <v>100</v>
+      </c>
+      <c r="AE32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>22</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="2">
+        <v>50</v>
+      </c>
+      <c r="M33" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="X33">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33">
+        <v>150</v>
+      </c>
+      <c r="AE33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="H34" s="2"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="M34" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="X34">
+        <v>4</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="2">
+        <v>150</v>
+      </c>
+      <c r="AE34" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="2">
+        <v>50</v>
+      </c>
+      <c r="M35" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="X35">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="2">
+        <v>200</v>
+      </c>
+      <c r="AE35" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="H36" s="2"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="M36" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="X36">
+        <v>6</v>
+      </c>
+      <c r="Z36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="2">
+        <v>670</v>
+      </c>
+      <c r="AE36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>24</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37">
+        <v>50</v>
+      </c>
+      <c r="M37" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="X37">
+        <v>7</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" s="2"/>
+    </row>
+    <row r="38" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="H38" s="2"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="M38" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="X38">
+        <v>8</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" s="2"/>
+    </row>
+    <row r="39" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>25</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39">
+        <v>50</v>
+      </c>
+      <c r="M39" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="X39">
+        <v>9</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="2">
+        <v>125</v>
+      </c>
+      <c r="AE39" s="2"/>
+    </row>
+    <row r="40" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="H40" s="2"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="M40" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="X40">
+        <v>10</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="2">
+        <v>125</v>
+      </c>
+      <c r="AE40" s="2"/>
+    </row>
+    <row r="41" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>26</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41">
+        <v>150</v>
+      </c>
+      <c r="M41" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="X41">
+        <v>11</v>
+      </c>
+      <c r="Z41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA41" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="2">
+        <v>175</v>
+      </c>
+      <c r="AE41" s="2"/>
+    </row>
+    <row r="42" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>27</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42">
+        <v>150</v>
+      </c>
+      <c r="M42" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="X42">
+        <v>12</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="2">
+        <v>175</v>
+      </c>
+      <c r="AE42" s="2"/>
+    </row>
+    <row r="43" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>28</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43">
+        <v>150</v>
+      </c>
+      <c r="M43" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="X43">
+        <v>13</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD43">
+        <v>50</v>
+      </c>
+      <c r="AE43" s="2"/>
+    </row>
+    <row r="44" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>29</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44">
+        <v>150</v>
+      </c>
+      <c r="M44" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+    </row>
+    <row r="45" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45">
+        <v>150</v>
+      </c>
+      <c r="M45" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+    </row>
+    <row r="46" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="Q46" s="2"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+    </row>
+    <row r="47" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="Q47" s="2"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+    </row>
+    <row r="48" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="Q48" s="2"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="V48" s="2"/>
+    </row>
+    <row r="49" spans="17:22" x14ac:dyDescent="0.25">
+      <c r="Q49" s="2"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="V49" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="138">
+    <mergeCell ref="R49:T49"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="R45:T45"/>
+    <mergeCell ref="R46:T46"/>
+    <mergeCell ref="R47:T47"/>
+    <mergeCell ref="R48:T48"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="R42:T42"/>
+    <mergeCell ref="AI7:AL7"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AJ12:AL12"/>
+    <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="AA42:AC42"/>
+    <mergeCell ref="AA34:AC34"/>
+    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AJ16:AL16"/>
+    <mergeCell ref="AA40:AC40"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AJ20:AL20"/>
+    <mergeCell ref="AJ21:AL21"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AA37:AC37"/>
+    <mergeCell ref="AA39:AC39"/>
+    <mergeCell ref="AA41:AC41"/>
+    <mergeCell ref="AA38:AC38"/>
+    <mergeCell ref="AA9:AC9"/>
+    <mergeCell ref="AA8:AC8"/>
+    <mergeCell ref="Z29:AC29"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AA31:AC31"/>
+    <mergeCell ref="AA33:AC33"/>
+    <mergeCell ref="AA24:AC24"/>
+    <mergeCell ref="AA25:AC25"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AA10:AC10"/>
+    <mergeCell ref="AA18:AC18"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="AA20:AC20"/>
+    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="AA22:AC22"/>
+    <mergeCell ref="AA23:AC23"/>
+    <mergeCell ref="AA12:AC12"/>
+    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="AA15:AC15"/>
+    <mergeCell ref="AA16:AC16"/>
+    <mergeCell ref="AA17:AC17"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="AA7:AC7"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="R13:T13"/>
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="I27:K27"/>
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="I29:K29"/>
     <mergeCell ref="I30:K30"/>
+    <mergeCell ref="Q7:T7"/>
     <mergeCell ref="I20:K20"/>
     <mergeCell ref="I21:K21"/>
     <mergeCell ref="I22:K22"/>

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6363B6A6-75BD-4727-AE81-134ED8895B9D}"/>
+  <xr:revisionPtr revIDLastSave="426" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF46848A-E2EC-4D40-9663-52D3E8FF5A9B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="112">
   <si>
     <t>A</t>
   </si>
@@ -341,14 +341,47 @@
     <t>DD</t>
   </si>
   <si>
-    <t>bonus B RNDOM SHIT?</t>
+    <t>bonus B DIFFERENT SHI ON START OF THE TURN</t>
+  </si>
+  <si>
+    <t>TURN START: AA IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: BB IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: CC IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: DD IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: EE IN HAND</t>
+  </si>
+  <si>
+    <t>A A A A</t>
+  </si>
+  <si>
+    <t>TURN START: PER CARD ON COUNTDOWN</t>
+  </si>
+  <si>
+    <t>TURN START: 1 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: 2 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>TURN START: 3 SUIT CARD IN HAND</t>
+  </si>
+  <si>
+    <t>EE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,13 +389,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -374,10 +419,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,8 +431,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -720,13 +774,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC38A9E3-0959-4F47-9569-6C1D59F951C2}">
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="20" max="20" width="21.140625" customWidth="1"/>
     <col min="29" max="29" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40">
       <c r="P2" t="s">
         <v>40</v>
       </c>
@@ -757,7 +812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40">
       <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
@@ -766,7 +821,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40">
       <c r="F4" t="s">
         <v>64</v>
       </c>
@@ -794,22 +849,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F5">
+    <row r="5" spans="1:40">
+      <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="2">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="4">
         <v>100</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="4">
         <v>0</v>
       </c>
       <c r="P5" t="s">
@@ -819,22 +875,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="s">
+    <row r="6" spans="1:40">
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="2">
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="4">
         <v>100</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="4">
         <v>0</v>
       </c>
       <c r="P6" t="s">
@@ -851,22 +908,23 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="2"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
+    <row r="7" spans="1:40">
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="2">
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="4">
         <v>100</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="4">
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
@@ -904,22 +962,23 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F8">
+    <row r="8" spans="1:40">
+      <c r="F8" s="3">
         <v>4</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="G8" s="3"/>
+      <c r="H8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="2">
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="4">
         <v>100</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="4">
         <v>0</v>
       </c>
       <c r="O8" t="s">
@@ -981,22 +1040,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F9">
+    <row r="9" spans="1:40">
+      <c r="F9" s="3">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="G9" s="3"/>
+      <c r="H9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="2">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="4">
         <v>100</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="4">
         <v>0</v>
       </c>
       <c r="O9">
@@ -1049,22 +1109,23 @@
       </c>
       <c r="AN9" s="2"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F10">
+    <row r="10" spans="1:40">
+      <c r="F10" s="3">
         <v>6</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="G10" s="3"/>
+      <c r="H10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="2">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="4">
         <v>100</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="4">
         <v>0</v>
       </c>
       <c r="Q10" s="2"/>
@@ -1096,22 +1157,23 @@
       </c>
       <c r="AN10" s="2"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F11">
+    <row r="11" spans="1:40">
+      <c r="F11" s="3">
         <v>7</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="G11" s="3"/>
+      <c r="H11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="2">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="4">
         <v>100</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="4">
         <v>0</v>
       </c>
       <c r="O11">
@@ -1164,22 +1226,23 @@
       </c>
       <c r="AN11" s="2"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F12">
+    <row r="12" spans="1:40">
+      <c r="F12" s="3">
         <v>8</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="G12" s="3"/>
+      <c r="H12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="2">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="4">
         <v>100</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="4">
         <v>0</v>
       </c>
       <c r="Q12" s="2"/>
@@ -1211,22 +1274,23 @@
       </c>
       <c r="AN12" s="2"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F13">
+    <row r="13" spans="1:40">
+      <c r="F13" s="3">
         <v>9</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="G13" s="3"/>
+      <c r="H13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="2">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="4">
         <v>100</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="4">
         <v>0</v>
       </c>
       <c r="O13">
@@ -1279,22 +1343,23 @@
       </c>
       <c r="AN13" s="2"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F14">
+    <row r="14" spans="1:40">
+      <c r="F14" s="3">
         <v>10</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="G14" s="3"/>
+      <c r="H14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="2">
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="4">
         <v>100</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="4">
         <v>0</v>
       </c>
       <c r="Q14" s="2"/>
@@ -1326,22 +1391,23 @@
       </c>
       <c r="AN14" s="2"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F15">
+    <row r="15" spans="1:40">
+      <c r="F15" s="3">
         <v>11</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="2">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="4">
         <v>200</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="4">
         <v>0</v>
       </c>
       <c r="O15">
@@ -1394,22 +1460,23 @@
       </c>
       <c r="AN15" s="2"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="F16">
+    <row r="16" spans="1:40">
+      <c r="F16" s="3">
         <v>12</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="3"/>
+      <c r="H16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="2">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="4">
         <v>200</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="4">
         <v>0</v>
       </c>
       <c r="Q16" s="2"/>
@@ -1441,22 +1508,23 @@
       </c>
       <c r="AN16" s="2"/>
     </row>
-    <row r="17" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F17">
+    <row r="17" spans="6:40">
+      <c r="F17" s="3">
         <v>13</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="G17" s="3"/>
+      <c r="H17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="2">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="4">
         <v>200</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="4">
         <v>0</v>
       </c>
       <c r="O17">
@@ -1509,22 +1577,23 @@
       </c>
       <c r="AN17" s="2"/>
     </row>
-    <row r="18" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F18">
+    <row r="18" spans="6:40">
+      <c r="F18" s="3">
         <v>14</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="G18" s="3"/>
+      <c r="H18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2">
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="4">
         <v>200</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="4">
         <v>0</v>
       </c>
       <c r="Q18" s="2"/>
@@ -1556,22 +1625,23 @@
       </c>
       <c r="AN18" s="2"/>
     </row>
-    <row r="19" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F19">
+    <row r="19" spans="6:40">
+      <c r="F19" s="3">
         <v>15</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="G19" s="3"/>
+      <c r="H19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="2">
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="4">
         <v>200</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" s="4">
         <v>0</v>
       </c>
       <c r="O19">
@@ -1624,23 +1694,23 @@
       </c>
       <c r="AN19" s="2"/>
     </row>
-    <row r="20" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F20">
+    <row r="20" spans="6:40">
+      <c r="F20" s="3">
         <v>16</v>
       </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="G20" s="3">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="2">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="4">
         <v>50</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20" s="4">
         <v>0</v>
       </c>
       <c r="O20">
@@ -1693,23 +1763,23 @@
       </c>
       <c r="AN20" s="2"/>
     </row>
-    <row r="21" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F21">
+    <row r="21" spans="6:40">
+      <c r="F21" s="3">
         <v>17</v>
       </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="2">
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="4">
         <v>50</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="4">
         <v>0</v>
       </c>
       <c r="O21">
@@ -1762,23 +1832,23 @@
       </c>
       <c r="AN21" s="2"/>
     </row>
-    <row r="22" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F22">
+    <row r="22" spans="6:40">
+      <c r="F22" s="3">
         <v>18</v>
       </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22" s="2" t="s">
+      <c r="G22" s="3">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="2">
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="4">
         <v>50</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="4">
         <v>0</v>
       </c>
       <c r="O22">
@@ -1831,23 +1901,23 @@
       </c>
       <c r="AN22" s="2"/>
     </row>
-    <row r="23" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F23">
+    <row r="23" spans="6:40">
+      <c r="F23" s="3">
         <v>19</v>
       </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" s="2" t="s">
+      <c r="G23" s="3">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="2">
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="4">
         <v>50</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="4">
         <v>0</v>
       </c>
       <c r="O23">
@@ -1900,23 +1970,23 @@
       </c>
       <c r="AN23" s="2"/>
     </row>
-    <row r="24" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F24">
+    <row r="24" spans="6:40">
+      <c r="F24" s="3">
         <v>20</v>
       </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="G24" s="3">
+        <v>2</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="2">
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="4">
         <v>50</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="4">
         <v>0</v>
       </c>
       <c r="O24">
@@ -1961,7 +2031,7 @@
       </c>
       <c r="AN24" s="2"/>
     </row>
-    <row r="25" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:40">
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1990,7 +2060,7 @@
       <c r="AC25" s="1"/>
       <c r="AE25" s="2"/>
     </row>
-    <row r="26" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:40">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2027,7 +2097,7 @@
       <c r="AC26" s="1"/>
       <c r="AE26" s="2"/>
     </row>
-    <row r="27" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:40">
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2059,7 +2129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:40">
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2076,7 +2146,7 @@
       <c r="T28" s="1"/>
       <c r="V28" s="2"/>
     </row>
-    <row r="29" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:40">
       <c r="H29" s="2"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2102,7 +2172,7 @@
       <c r="AC29" s="1"/>
       <c r="AD29" s="2"/>
     </row>
-    <row r="30" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:40">
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -2154,7 +2224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:40">
       <c r="F31">
         <v>21</v>
       </c>
@@ -2172,12 +2242,23 @@
       <c r="M31" s="2">
         <v>2</v>
       </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="1"/>
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
+      <c r="U31" s="2">
+        <v>25</v>
+      </c>
+      <c r="V31" s="2">
+        <v>3</v>
+      </c>
       <c r="X31">
         <v>1</v>
       </c>
@@ -2196,7 +2277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="6:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:40">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -2204,12 +2285,23 @@
       <c r="M32" s="2">
         <v>2</v>
       </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="1"/>
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
+      <c r="U32" s="2">
+        <v>25</v>
+      </c>
+      <c r="V32" s="2">
+        <v>3</v>
+      </c>
       <c r="X32">
         <v>2</v>
       </c>
@@ -2228,7 +2320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:31">
       <c r="F33">
         <v>22</v>
       </c>
@@ -2246,12 +2338,23 @@
       <c r="M33" s="2">
         <v>2</v>
       </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="1"/>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
+      <c r="U33" s="2">
+        <v>25</v>
+      </c>
+      <c r="V33" s="2">
+        <v>3</v>
+      </c>
       <c r="X33">
         <v>3</v>
       </c>
@@ -2270,7 +2373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:31">
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2278,12 +2381,23 @@
       <c r="M34" s="2">
         <v>2</v>
       </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="1"/>
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
+      <c r="U34" s="2">
+        <v>25</v>
+      </c>
+      <c r="V34" s="2">
+        <v>3</v>
+      </c>
       <c r="X34">
         <v>4</v>
       </c>
@@ -2302,7 +2416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:31">
       <c r="F35">
         <v>23</v>
       </c>
@@ -2320,12 +2434,26 @@
       <c r="M35" s="2">
         <v>2</v>
       </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="1"/>
+      <c r="O35">
+        <v>5</v>
+      </c>
+      <c r="P35" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
+      <c r="U35" s="2">
+        <v>25</v>
+      </c>
+      <c r="V35" s="2">
+        <v>3</v>
+      </c>
       <c r="X35">
         <v>5</v>
       </c>
@@ -2344,7 +2472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:31">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2352,12 +2480,23 @@
       <c r="M36" s="2">
         <v>2</v>
       </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="1"/>
+      <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
+      <c r="U36" s="2">
+        <v>25</v>
+      </c>
+      <c r="V36" s="2">
+        <v>4</v>
+      </c>
       <c r="X36">
         <v>6</v>
       </c>
@@ -2376,7 +2515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:31">
       <c r="F37">
         <v>24</v>
       </c>
@@ -2394,12 +2533,23 @@
       <c r="M37" s="2">
         <v>2</v>
       </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="1"/>
+      <c r="O37">
+        <v>7</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
+      <c r="U37" s="2">
+        <v>25</v>
+      </c>
+      <c r="V37" s="2">
+        <v>3</v>
+      </c>
       <c r="X37">
         <v>7</v>
       </c>
@@ -2416,7 +2566,7 @@
       </c>
       <c r="AE37" s="2"/>
     </row>
-    <row r="38" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:31">
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2424,12 +2574,23 @@
       <c r="M38" s="2">
         <v>2</v>
       </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="1"/>
+      <c r="O38">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
+      <c r="U38" s="2">
+        <v>50</v>
+      </c>
+      <c r="V38" s="2">
+        <v>3</v>
+      </c>
       <c r="X38">
         <v>8</v>
       </c>
@@ -2446,7 +2607,7 @@
       </c>
       <c r="AE38" s="2"/>
     </row>
-    <row r="39" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:31">
       <c r="F39">
         <v>25</v>
       </c>
@@ -2464,12 +2625,23 @@
       <c r="M39" s="2">
         <v>2</v>
       </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="1"/>
+      <c r="O39">
+        <v>9</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
+      <c r="U39" s="2">
+        <v>75</v>
+      </c>
+      <c r="V39" s="2">
+        <v>3</v>
+      </c>
       <c r="X39">
         <v>9</v>
       </c>
@@ -2486,7 +2658,7 @@
       </c>
       <c r="AE39" s="2"/>
     </row>
-    <row r="40" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:31">
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -2494,12 +2666,23 @@
       <c r="M40" s="2">
         <v>2</v>
       </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="1"/>
+      <c r="O40">
+        <v>10</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="2"/>
+      <c r="U40" s="2">
+        <v>25</v>
+      </c>
+      <c r="V40" s="2">
+        <v>4</v>
+      </c>
       <c r="X40">
         <v>10</v>
       </c>
@@ -2516,7 +2699,7 @@
       </c>
       <c r="AE40" s="2"/>
     </row>
-    <row r="41" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:31">
       <c r="F41">
         <v>26</v>
       </c>
@@ -2534,12 +2717,23 @@
       <c r="M41" s="2">
         <v>3</v>
       </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="1"/>
+      <c r="O41">
+        <v>11</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
+      <c r="U41" s="2">
+        <v>25</v>
+      </c>
+      <c r="V41" s="2">
+        <v>3</v>
+      </c>
       <c r="X41">
         <v>11</v>
       </c>
@@ -2556,7 +2750,7 @@
       </c>
       <c r="AE41" s="2"/>
     </row>
-    <row r="42" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:31">
       <c r="F42">
         <v>27</v>
       </c>
@@ -2574,12 +2768,23 @@
       <c r="M42" s="2">
         <v>3</v>
       </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="1"/>
+      <c r="O42">
+        <v>12</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="2"/>
+      <c r="U42" s="2">
+        <v>50</v>
+      </c>
+      <c r="V42" s="2">
+        <v>3</v>
+      </c>
       <c r="X42">
         <v>12</v>
       </c>
@@ -2596,7 +2801,7 @@
       </c>
       <c r="AE42" s="2"/>
     </row>
-    <row r="43" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:31">
       <c r="F43">
         <v>28</v>
       </c>
@@ -2614,12 +2819,23 @@
       <c r="M43" s="2">
         <v>3</v>
       </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="1"/>
+      <c r="O43">
+        <v>13</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="2"/>
+      <c r="U43" s="2">
+        <v>75</v>
+      </c>
+      <c r="V43" s="2">
+        <v>3</v>
+      </c>
       <c r="X43">
         <v>13</v>
       </c>
@@ -2631,7 +2847,7 @@
       </c>
       <c r="AE43" s="2"/>
     </row>
-    <row r="44" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:31">
       <c r="F44">
         <v>29</v>
       </c>
@@ -2649,14 +2865,23 @@
       <c r="M44" s="2">
         <v>3</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="O44">
+        <v>14</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="2"/>
-    </row>
-    <row r="45" spans="6:31" x14ac:dyDescent="0.25">
+      <c r="U44" s="2">
+        <v>50</v>
+      </c>
+      <c r="V44" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="6:31">
       <c r="F45">
         <v>30</v>
       </c>
@@ -2673,6 +2898,9 @@
       </c>
       <c r="M45" s="2">
         <v>3</v>
+      </c>
+      <c r="O45">
+        <v>15</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" s="1"/>
@@ -2681,15 +2909,17 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
     </row>
-    <row r="46" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="Q46" s="2"/>
+    <row r="46" spans="6:31">
+      <c r="O46">
+        <v>16</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
     </row>
-    <row r="47" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:31">
       <c r="Q47" s="2"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -2697,14 +2927,14 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
     </row>
-    <row r="48" spans="6:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:31">
       <c r="Q48" s="2"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="V48" s="2"/>
     </row>
-    <row r="49" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="17:22">
       <c r="Q49" s="2"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF46848A-E2EC-4D40-9663-52D3E8FF5A9B}"/>
+  <xr:revisionPtr revIDLastSave="433" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE89B2A-EF7A-4DB0-9914-3CE3E5C03D8E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -381,7 +381,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,14 +774,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC38A9E3-0959-4F47-9569-6C1D59F951C2}">
   <dimension ref="A1:AN49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="11.28515625" customWidth="1"/>
     <col min="20" max="20" width="21.140625" customWidth="1"/>
-    <col min="29" max="29" width="12.7109375" customWidth="1"/>
+    <col min="29" max="29" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -804,7 +804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="P2" t="s">
         <v>40</v>
       </c>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
@@ -821,7 +821,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>64</v>
       </c>
@@ -849,7 +849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F5" s="3">
         <v>1</v>
       </c>
@@ -875,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F6" s="3">
         <v>2</v>
       </c>
@@ -908,7 +908,7 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="2"/>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F7" s="3">
         <v>3</v>
       </c>
@@ -962,7 +962,7 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2"/>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F8" s="3">
         <v>4</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F9" s="3">
         <v>5</v>
       </c>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AN9" s="2"/>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F10" s="3">
         <v>6</v>
       </c>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AN10" s="2"/>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F11" s="3">
         <v>7</v>
       </c>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AN11" s="2"/>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F12" s="3">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AN12" s="2"/>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F13" s="3">
         <v>9</v>
       </c>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AN13" s="2"/>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F14" s="3">
         <v>10</v>
       </c>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AN14" s="2"/>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F15" s="3">
         <v>11</v>
       </c>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AN15" s="2"/>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="F16" s="3">
         <v>12</v>
       </c>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AN16" s="2"/>
     </row>
-    <row r="17" spans="6:40">
+    <row r="17" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F17" s="3">
         <v>13</v>
       </c>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="AN17" s="2"/>
     </row>
-    <row r="18" spans="6:40">
+    <row r="18" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F18" s="3">
         <v>14</v>
       </c>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AN18" s="2"/>
     </row>
-    <row r="19" spans="6:40">
+    <row r="19" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F19" s="3">
         <v>15</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="AN19" s="2"/>
     </row>
-    <row r="20" spans="6:40">
+    <row r="20" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F20" s="3">
         <v>16</v>
       </c>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AN20" s="2"/>
     </row>
-    <row r="21" spans="6:40">
+    <row r="21" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F21" s="3">
         <v>17</v>
       </c>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AN21" s="2"/>
     </row>
-    <row r="22" spans="6:40">
+    <row r="22" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F22" s="3">
         <v>18</v>
       </c>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AN22" s="2"/>
     </row>
-    <row r="23" spans="6:40">
+    <row r="23" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F23" s="3">
         <v>19</v>
       </c>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AN23" s="2"/>
     </row>
-    <row r="24" spans="6:40">
+    <row r="24" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F24" s="3">
         <v>20</v>
       </c>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="AN24" s="2"/>
     </row>
-    <row r="25" spans="6:40">
+    <row r="25" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H25" s="2"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2060,7 +2060,7 @@
       <c r="AC25" s="1"/>
       <c r="AE25" s="2"/>
     </row>
-    <row r="26" spans="6:40">
+    <row r="26" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2097,7 +2097,7 @@
       <c r="AC26" s="1"/>
       <c r="AE26" s="2"/>
     </row>
-    <row r="27" spans="6:40">
+    <row r="27" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H27" s="2"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2129,7 +2129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="6:40">
+    <row r="28" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H28" s="2"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2146,7 +2146,7 @@
       <c r="T28" s="1"/>
       <c r="V28" s="2"/>
     </row>
-    <row r="29" spans="6:40">
+    <row r="29" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H29" s="2"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2172,7 +2172,7 @@
       <c r="AC29" s="1"/>
       <c r="AD29" s="2"/>
     </row>
-    <row r="30" spans="6:40">
+    <row r="30" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H30" s="2"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -2224,7 +2224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="6:40">
+    <row r="31" spans="6:40" x14ac:dyDescent="0.25">
       <c r="F31">
         <v>21</v>
       </c>
@@ -2271,13 +2271,13 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AE31" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="6:40">
+    <row r="32" spans="6:40" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -2314,13 +2314,13 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AE32" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="6:31">
+    <row r="33" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F33">
         <v>22</v>
       </c>
@@ -2367,13 +2367,13 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AE33" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="6:31">
+    <row r="34" spans="6:31" x14ac:dyDescent="0.25">
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2410,13 +2410,13 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="2">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AE34" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="6:31">
+    <row r="35" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F35">
         <v>23</v>
       </c>
@@ -2466,13 +2466,13 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="2">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="AE35" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="6:31">
+    <row r="36" spans="6:31" x14ac:dyDescent="0.25">
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="6:31">
+    <row r="37" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F37">
         <v>24</v>
       </c>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AE37" s="2"/>
     </row>
-    <row r="38" spans="6:31">
+    <row r="38" spans="6:31" x14ac:dyDescent="0.25">
       <c r="H38" s="2"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AE38" s="2"/>
     </row>
-    <row r="39" spans="6:31">
+    <row r="39" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F39">
         <v>25</v>
       </c>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AE39" s="2"/>
     </row>
-    <row r="40" spans="6:31">
+    <row r="40" spans="6:31" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AE40" s="2"/>
     </row>
-    <row r="41" spans="6:31">
+    <row r="41" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F41">
         <v>26</v>
       </c>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AE41" s="2"/>
     </row>
-    <row r="42" spans="6:31">
+    <row r="42" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F42">
         <v>27</v>
       </c>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AE42" s="2"/>
     </row>
-    <row r="43" spans="6:31">
+    <row r="43" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F43">
         <v>28</v>
       </c>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AE43" s="2"/>
     </row>
-    <row r="44" spans="6:31">
+    <row r="44" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F44">
         <v>29</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="6:31">
+    <row r="45" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F45">
         <v>30</v>
       </c>
@@ -2909,7 +2909,7 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
     </row>
-    <row r="46" spans="6:31">
+    <row r="46" spans="6:31" x14ac:dyDescent="0.25">
       <c r="O46">
         <v>16</v>
       </c>
@@ -2919,7 +2919,7 @@
       <c r="U46" s="2"/>
       <c r="V46" s="2"/>
     </row>
-    <row r="47" spans="6:31">
+    <row r="47" spans="6:31" x14ac:dyDescent="0.25">
       <c r="Q47" s="2"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -2927,14 +2927,14 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
     </row>
-    <row r="48" spans="6:31">
+    <row r="48" spans="6:31" x14ac:dyDescent="0.25">
       <c r="Q48" s="2"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="V48" s="2"/>
     </row>
-    <row r="49" spans="17:22">
+    <row r="49" spans="17:22" x14ac:dyDescent="0.25">
       <c r="Q49" s="2"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE89B2A-EF7A-4DB0-9914-3CE3E5C03D8E}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3BBDF79-7762-456D-8D3E-9DF5D5D767AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -381,7 +381,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,8 +396,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +421,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -419,11 +443,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -438,9 +464,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -981,44 +1023,44 @@
       <c r="M8" s="4">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" t="s">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="V8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="X8">
-        <v>3</v>
-      </c>
-      <c r="Y8">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="2" t="s">
+      <c r="X8" s="9">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AA8" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="2">
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="10">
         <v>150</v>
       </c>
-      <c r="AE8" s="2"/>
+      <c r="AE8" s="10"/>
       <c r="AG8" t="s">
         <v>64</v>
       </c>
@@ -1059,52 +1101,55 @@
       <c r="M9" s="4">
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="6">
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="P9" s="6"/>
+      <c r="Q9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="2">
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="7">
         <v>125</v>
       </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9">
+      <c r="V9" s="7">
+        <v>0</v>
+      </c>
+      <c r="X9" s="6">
         <v>4</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AA9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="2">
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="7">
         <v>75</v>
       </c>
-      <c r="AE9" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG9">
+      <c r="AE9" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="9">
         <v>1</v>
       </c>
-      <c r="AI9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
-      <c r="AM9" s="2">
+      <c r="AK9" s="11"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="10">
         <v>175</v>
       </c>
       <c r="AN9" s="2"/>
@@ -1128,31 +1173,37 @@
       <c r="M10" s="4">
         <v>0</v>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AE10" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG10">
-        <v>2</v>
-      </c>
-      <c r="AI10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG10" s="9">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="1"/>
-      <c r="AM10" s="2">
+      <c r="AK10" s="11"/>
+      <c r="AL10" s="11"/>
+      <c r="AM10" s="10">
         <v>175</v>
       </c>
       <c r="AN10" s="2"/>
@@ -1176,52 +1227,55 @@
       <c r="M11" s="4">
         <v>0</v>
       </c>
-      <c r="O11">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+      <c r="O11" s="6">
+        <v>2</v>
+      </c>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="R11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="2">
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="7">
         <v>125</v>
       </c>
-      <c r="V11" s="2">
-        <v>0</v>
-      </c>
-      <c r="X11">
+      <c r="V11" s="7">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6">
         <v>5</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1" t="s">
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="2">
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="7">
         <v>75</v>
       </c>
-      <c r="AE11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG11">
-        <v>3</v>
-      </c>
-      <c r="AI11" s="2" t="s">
+      <c r="AE11" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="9">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="9"/>
+      <c r="AI11" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AJ11" s="1" t="s">
+      <c r="AJ11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
-      <c r="AM11" s="2">
+      <c r="AK11" s="11"/>
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="10">
         <v>175</v>
       </c>
       <c r="AN11" s="2"/>
@@ -1245,31 +1299,37 @@
       <c r="M12" s="4">
         <v>0</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AE12" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG12">
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="9">
         <v>4</v>
       </c>
-      <c r="AI12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
+      <c r="AH12" s="9"/>
+      <c r="AI12" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="2">
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="11"/>
+      <c r="AM12" s="10">
         <v>175</v>
       </c>
       <c r="AN12" s="2"/>
@@ -1293,52 +1353,55 @@
       <c r="M13" s="4">
         <v>0</v>
       </c>
-      <c r="O13">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R13" s="1" t="s">
+      <c r="O13" s="6">
+        <v>3</v>
+      </c>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="2">
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="7">
         <v>125</v>
       </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="V13" s="7">
+        <v>0</v>
+      </c>
+      <c r="X13" s="6">
         <v>6</v>
       </c>
-      <c r="Z13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="1" t="s">
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="2">
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="7">
         <v>75</v>
       </c>
-      <c r="AE13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG13">
+      <c r="AE13" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="9">
         <v>5</v>
       </c>
-      <c r="AI13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="1"/>
-      <c r="AM13" s="2">
+      <c r="AK13" s="11"/>
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="10">
         <v>175</v>
       </c>
       <c r="AN13" s="2"/>
@@ -1362,31 +1425,37 @@
       <c r="M14" s="4">
         <v>0</v>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AE14" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG14">
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="9">
         <v>6</v>
       </c>
-      <c r="AI14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ14" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
-      <c r="AM14" s="2">
+      <c r="AK14" s="11"/>
+      <c r="AL14" s="11"/>
+      <c r="AM14" s="10">
         <v>275</v>
       </c>
       <c r="AN14" s="2"/>
@@ -1410,52 +1479,55 @@
       <c r="M15" s="4">
         <v>0</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="6">
         <v>4</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="P15" s="6"/>
+      <c r="Q15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="2">
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="7">
         <v>125</v>
       </c>
-      <c r="V15" s="2">
-        <v>0</v>
-      </c>
-      <c r="X15">
+      <c r="V15" s="7">
+        <v>0</v>
+      </c>
+      <c r="X15" s="6">
         <v>7</v>
       </c>
-      <c r="Z15" s="2" t="s">
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="AA15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15">
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="6">
         <v>75</v>
       </c>
-      <c r="AE15" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG15">
+      <c r="AE15" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="9">
         <v>7</v>
       </c>
-      <c r="AI15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
-      <c r="AM15" s="2">
+      <c r="AK15" s="11"/>
+      <c r="AL15" s="11"/>
+      <c r="AM15" s="10">
         <v>275</v>
       </c>
       <c r="AN15" s="2"/>
@@ -1479,31 +1551,37 @@
       <c r="M16" s="4">
         <v>0</v>
       </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AE16" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG16">
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG16" s="9">
         <v>8</v>
       </c>
-      <c r="AI16" s="2" t="s">
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="1" t="s">
+      <c r="AJ16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
-      <c r="AM16" s="2">
+      <c r="AK16" s="11"/>
+      <c r="AL16" s="11"/>
+      <c r="AM16" s="10">
         <v>275</v>
       </c>
       <c r="AN16" s="2"/>
@@ -1527,52 +1605,55 @@
       <c r="M17" s="4">
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="6">
         <v>5</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="1" t="s">
+      <c r="P17" s="6"/>
+      <c r="Q17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="2">
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="7">
         <v>125</v>
       </c>
-      <c r="V17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17">
+      <c r="V17" s="7">
+        <v>0</v>
+      </c>
+      <c r="X17" s="6">
         <v>8</v>
       </c>
-      <c r="Z17" s="2" t="s">
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AA17" s="1" t="s">
+      <c r="AA17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17">
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="6">
         <v>75</v>
       </c>
-      <c r="AE17" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG17">
+      <c r="AE17" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG17" s="9">
         <v>9</v>
       </c>
-      <c r="AI17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ17" s="1" t="s">
+      <c r="AH17" s="9"/>
+      <c r="AI17" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
-      <c r="AM17" s="2">
+      <c r="AK17" s="11"/>
+      <c r="AL17" s="11"/>
+      <c r="AM17" s="10">
         <v>275</v>
       </c>
       <c r="AN17" s="2"/>
@@ -1596,31 +1677,37 @@
       <c r="M18" s="4">
         <v>0</v>
       </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AE18" s="2">
-        <v>2</v>
-      </c>
-      <c r="AG18">
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="7">
+        <v>2</v>
+      </c>
+      <c r="AG18" s="9">
         <v>10</v>
       </c>
-      <c r="AI18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-      <c r="AM18" s="2">
+      <c r="AK18" s="11"/>
+      <c r="AL18" s="11"/>
+      <c r="AM18" s="10">
         <v>275</v>
       </c>
       <c r="AN18" s="2"/>
@@ -1644,52 +1731,55 @@
       <c r="M19" s="4">
         <v>0</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="6">
         <v>6</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="P19" s="6"/>
+      <c r="Q19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="R19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="2">
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="7">
         <v>250</v>
       </c>
-      <c r="V19" s="2">
-        <v>0</v>
-      </c>
-      <c r="X19">
+      <c r="V19" s="7">
+        <v>0</v>
+      </c>
+      <c r="X19" s="6">
         <v>9</v>
       </c>
-      <c r="Z19" s="2" t="s">
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AA19" s="1" t="s">
+      <c r="AA19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19">
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="6">
         <v>175</v>
       </c>
-      <c r="AE19" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG19">
+      <c r="AE19" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="9">
         <v>11</v>
       </c>
-      <c r="AI19" s="2" t="s">
+      <c r="AH19" s="9"/>
+      <c r="AI19" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="AJ19" s="1" t="s">
+      <c r="AJ19" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
-      <c r="AM19" s="2">
+      <c r="AK19" s="11"/>
+      <c r="AL19" s="11"/>
+      <c r="AM19" s="10">
         <v>425</v>
       </c>
       <c r="AN19" s="2"/>
@@ -1713,52 +1803,55 @@
       <c r="M20" s="4">
         <v>0</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="6">
         <v>7</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="P20" s="6"/>
+      <c r="Q20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="R20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="2">
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="7">
         <v>250</v>
       </c>
-      <c r="V20" s="2">
-        <v>0</v>
-      </c>
-      <c r="X20">
+      <c r="V20" s="7">
+        <v>0</v>
+      </c>
+      <c r="X20" s="6">
         <v>10</v>
       </c>
-      <c r="Z20" s="2" t="s">
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AA20" s="1" t="s">
+      <c r="AA20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20">
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="6">
         <v>175</v>
       </c>
-      <c r="AE20" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG20">
+      <c r="AE20" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="9">
         <v>12</v>
       </c>
-      <c r="AI20" s="2" t="s">
+      <c r="AH20" s="9"/>
+      <c r="AI20" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="1" t="s">
+      <c r="AJ20" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
-      <c r="AM20" s="2">
+      <c r="AK20" s="11"/>
+      <c r="AL20" s="11"/>
+      <c r="AM20" s="10">
         <v>425</v>
       </c>
       <c r="AN20" s="2"/>
@@ -1782,52 +1875,55 @@
       <c r="M21" s="4">
         <v>0</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="6">
         <v>8</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="P21" s="6"/>
+      <c r="Q21" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="R21" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="2">
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="7">
         <v>250</v>
       </c>
-      <c r="V21" s="2">
-        <v>0</v>
-      </c>
-      <c r="X21">
+      <c r="V21" s="7">
+        <v>0</v>
+      </c>
+      <c r="X21" s="6">
         <v>11</v>
       </c>
-      <c r="Z21" s="2" t="s">
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AA21" s="1" t="s">
+      <c r="AA21" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21">
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="6">
         <v>175</v>
       </c>
-      <c r="AE21" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG21">
+      <c r="AE21" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="9">
         <v>13</v>
       </c>
-      <c r="AI21" s="2" t="s">
+      <c r="AH21" s="9"/>
+      <c r="AI21" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AJ21" s="1" t="s">
+      <c r="AJ21" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
-      <c r="AM21" s="2">
+      <c r="AK21" s="11"/>
+      <c r="AL21" s="11"/>
+      <c r="AM21" s="10">
         <v>425</v>
       </c>
       <c r="AN21" s="2"/>
@@ -1851,52 +1947,55 @@
       <c r="M22" s="4">
         <v>0</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="6">
         <v>9</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R22" s="1" t="s">
+      <c r="P22" s="6"/>
+      <c r="Q22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="2">
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="7">
         <v>250</v>
       </c>
-      <c r="V22" s="2">
-        <v>0</v>
-      </c>
-      <c r="X22">
+      <c r="V22" s="7">
+        <v>0</v>
+      </c>
+      <c r="X22" s="6">
         <v>12</v>
       </c>
-      <c r="Z22" s="2" t="s">
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AA22" s="1" t="s">
+      <c r="AA22" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22">
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="6">
         <v>175</v>
       </c>
-      <c r="AE22" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG22">
+      <c r="AE22" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG22" s="9">
         <v>14</v>
       </c>
-      <c r="AI22" s="2" t="s">
+      <c r="AH22" s="9"/>
+      <c r="AI22" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AJ22" s="1" t="s">
+      <c r="AJ22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
-      <c r="AM22" s="2">
+      <c r="AK22" s="11"/>
+      <c r="AL22" s="11"/>
+      <c r="AM22" s="10">
         <v>425</v>
       </c>
       <c r="AN22" s="2"/>
@@ -1920,52 +2019,55 @@
       <c r="M23" s="4">
         <v>0</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="6">
         <v>10</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="1" t="s">
+      <c r="P23" s="6"/>
+      <c r="Q23" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="2">
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="7">
         <v>250</v>
       </c>
-      <c r="V23" s="2">
-        <v>0</v>
-      </c>
-      <c r="X23">
+      <c r="V23" s="7">
+        <v>0</v>
+      </c>
+      <c r="X23" s="6">
         <v>13</v>
       </c>
-      <c r="Z23" s="2" t="s">
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AA23" s="1" t="s">
+      <c r="AA23" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23">
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8"/>
+      <c r="AD23" s="6">
         <v>175</v>
       </c>
-      <c r="AE23" s="2">
-        <v>3</v>
-      </c>
-      <c r="AG23">
+      <c r="AE23" s="7">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="9">
         <v>15</v>
       </c>
-      <c r="AI23" s="2" t="s">
+      <c r="AH23" s="9"/>
+      <c r="AI23" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="AJ23" s="1" t="s">
+      <c r="AJ23" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="2">
+      <c r="AK23" s="11"/>
+      <c r="AL23" s="11"/>
+      <c r="AM23" s="10">
         <v>425</v>
       </c>
       <c r="AN23" s="2"/>
@@ -1989,44 +2091,49 @@
       <c r="M24" s="4">
         <v>0</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="6">
         <v>11</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="6">
         <v>1</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="Q24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="2">
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="7">
         <v>50</v>
       </c>
-      <c r="V24" s="2">
-        <v>0</v>
-      </c>
-      <c r="X24">
+      <c r="V24" s="7">
+        <v>0</v>
+      </c>
+      <c r="X24" s="6">
         <v>14</v>
       </c>
-      <c r="Z24" s="2" t="s">
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="2">
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="7">
         <v>50</v>
       </c>
-      <c r="AE24" s="2"/>
-      <c r="AG24">
+      <c r="AE24" s="7"/>
+      <c r="AG24" s="9">
         <v>16</v>
       </c>
-      <c r="AI24" s="2" t="s">
+      <c r="AH24" s="9"/>
+      <c r="AI24" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="AM24" s="2">
+      <c r="AJ24" s="9"/>
+      <c r="AK24" s="9"/>
+      <c r="AL24" s="9"/>
+      <c r="AM24" s="10">
         <v>50</v>
       </c>
       <c r="AN24" s="2"/>
@@ -2042,18 +2149,18 @@
       <c r="M25" s="2">
         <v>0</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="6">
         <v>12</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
@@ -2071,24 +2178,24 @@
       <c r="M26" s="2">
         <v>0</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="6">
         <v>13</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="6">
         <v>1</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="Q26" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="R26" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26">
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="6">
         <v>175</v>
       </c>
-      <c r="V26" s="2">
+      <c r="V26" s="7">
         <v>3</v>
       </c>
       <c r="Z26" s="2"/>
@@ -2108,24 +2215,24 @@
       <c r="M27" s="2">
         <v>0</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="6">
         <v>14</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="6">
         <v>1</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="1" t="s">
+      <c r="Q27" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27">
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="6">
         <v>75</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2225,678 +2332,732 @@
       </c>
     </row>
     <row r="31" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="F31">
+      <c r="F31" s="6">
         <v>21</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="G31" s="6"/>
+      <c r="H31" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="2">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="7">
         <v>50</v>
       </c>
-      <c r="M31" s="2">
-        <v>2</v>
-      </c>
-      <c r="O31">
+      <c r="M31" s="7">
+        <v>2</v>
+      </c>
+      <c r="O31" s="9">
         <v>1</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R31" s="1" t="s">
+      <c r="P31" s="9"/>
+      <c r="Q31" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="R31" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="2">
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="10">
         <v>25</v>
       </c>
-      <c r="V31" s="2">
-        <v>3</v>
-      </c>
-      <c r="X31">
+      <c r="V31" s="10">
+        <v>3</v>
+      </c>
+      <c r="X31" s="9">
         <v>1</v>
       </c>
-      <c r="Z31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA31" s="1" t="s">
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="2">
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11"/>
+      <c r="AD31" s="10">
         <v>75</v>
       </c>
-      <c r="AE31" s="2">
+      <c r="AE31" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="6:40" x14ac:dyDescent="0.25">
-      <c r="H32" s="2"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="M32" s="2">
-        <v>2</v>
-      </c>
-      <c r="O32">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="1" t="s">
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="7">
+        <v>2</v>
+      </c>
+      <c r="O32" s="9">
+        <v>2</v>
+      </c>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="2">
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="10">
         <v>25</v>
       </c>
-      <c r="V32" s="2">
-        <v>3</v>
-      </c>
-      <c r="X32">
-        <v>2</v>
-      </c>
-      <c r="Z32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1" t="s">
+      <c r="V32" s="10">
+        <v>3</v>
+      </c>
+      <c r="X32" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="2">
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="10">
         <v>75</v>
       </c>
-      <c r="AE32" s="2">
+      <c r="AE32" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F33">
+      <c r="F33" s="6">
         <v>22</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="G33" s="6"/>
+      <c r="H33" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="2">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="7">
         <v>50</v>
       </c>
-      <c r="M33" s="2">
-        <v>2</v>
-      </c>
-      <c r="O33">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="2" t="s">
+      <c r="M33" s="7">
+        <v>2</v>
+      </c>
+      <c r="O33" s="9">
+        <v>3</v>
+      </c>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="R33" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="2">
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="10">
         <v>25</v>
       </c>
-      <c r="V33" s="2">
-        <v>3</v>
-      </c>
-      <c r="X33">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA33" s="1" t="s">
+      <c r="V33" s="10">
+        <v>3</v>
+      </c>
+      <c r="X33" s="9">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA33" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33">
+      <c r="AB33" s="11"/>
+      <c r="AC33" s="11"/>
+      <c r="AD33" s="9">
         <v>125</v>
       </c>
-      <c r="AE33" s="2">
+      <c r="AE33" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="M34" s="2">
-        <v>2</v>
-      </c>
-      <c r="O34">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="7">
+        <v>2</v>
+      </c>
+      <c r="O34" s="9">
         <v>4</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1" t="s">
+      <c r="P34" s="9"/>
+      <c r="Q34" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="2">
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="10">
         <v>25</v>
       </c>
-      <c r="V34" s="2">
-        <v>3</v>
-      </c>
-      <c r="X34">
+      <c r="V34" s="10">
+        <v>3</v>
+      </c>
+      <c r="X34" s="9">
         <v>4</v>
       </c>
-      <c r="Z34" s="2" t="s">
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="AA34" s="1" t="s">
+      <c r="AA34" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="2">
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+      <c r="AD34" s="10">
         <v>125</v>
       </c>
-      <c r="AE34" s="2">
+      <c r="AE34" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F35">
+      <c r="F35" s="6">
         <v>23</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="2">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="7">
         <v>50</v>
       </c>
-      <c r="M35" s="2">
-        <v>2</v>
-      </c>
-      <c r="O35">
+      <c r="M35" s="7">
+        <v>2</v>
+      </c>
+      <c r="O35" s="9">
         <v>5</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P35" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="Q35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1" t="s">
+      <c r="Q35" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="2">
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="10">
         <v>25</v>
       </c>
-      <c r="V35" s="2">
-        <v>3</v>
-      </c>
-      <c r="X35">
+      <c r="V35" s="10">
+        <v>3</v>
+      </c>
+      <c r="X35" s="9">
         <v>5</v>
       </c>
-      <c r="Z35" s="2" t="s">
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AA35" s="1" t="s">
+      <c r="AA35" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="2">
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="10">
         <v>175</v>
       </c>
-      <c r="AE35" s="2">
+      <c r="AE35" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="M36" s="2">
-        <v>2</v>
-      </c>
-      <c r="O36">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="7">
+        <v>2</v>
+      </c>
+      <c r="O36" s="9">
         <v>6</v>
       </c>
-      <c r="Q36" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1" t="s">
+      <c r="P36" s="9"/>
+      <c r="Q36" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R36" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="2">
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="10">
         <v>25</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V36" s="10">
         <v>4</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="9">
         <v>6</v>
       </c>
-      <c r="Z36" s="2" t="s">
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AA36" s="1" t="s">
+      <c r="AA36" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="2">
+      <c r="AB36" s="11"/>
+      <c r="AC36" s="11"/>
+      <c r="AD36" s="10">
         <v>670</v>
       </c>
-      <c r="AE36" s="2">
+      <c r="AE36" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F37">
+      <c r="F37" s="6">
         <v>24</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="G37" s="6"/>
+      <c r="H37" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37">
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="6">
         <v>50</v>
       </c>
-      <c r="M37" s="2">
-        <v>2</v>
-      </c>
-      <c r="O37">
+      <c r="M37" s="7">
+        <v>2</v>
+      </c>
+      <c r="O37" s="9">
         <v>7</v>
       </c>
-      <c r="Q37" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R37" s="1" t="s">
+      <c r="P37" s="9"/>
+      <c r="Q37" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R37" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="2">
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="10">
         <v>25</v>
       </c>
-      <c r="V37" s="2">
-        <v>3</v>
-      </c>
-      <c r="X37">
+      <c r="V37" s="10">
+        <v>3</v>
+      </c>
+      <c r="X37" s="9">
         <v>7</v>
       </c>
-      <c r="Z37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA37" s="1" t="s">
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA37" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="2">
+      <c r="AB37" s="11"/>
+      <c r="AC37" s="11"/>
+      <c r="AD37" s="10">
         <v>75</v>
       </c>
-      <c r="AE37" s="2"/>
+      <c r="AE37" s="10"/>
     </row>
     <row r="38" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="M38" s="2">
-        <v>2</v>
-      </c>
-      <c r="O38">
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="7">
+        <v>2</v>
+      </c>
+      <c r="O38" s="9">
         <v>8</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1" t="s">
+      <c r="P38" s="9"/>
+      <c r="Q38" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R38" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="2">
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="10">
         <v>50</v>
       </c>
-      <c r="V38" s="2">
-        <v>3</v>
-      </c>
-      <c r="X38">
+      <c r="V38" s="10">
+        <v>3</v>
+      </c>
+      <c r="X38" s="9">
         <v>8</v>
       </c>
-      <c r="Z38" s="2" t="s">
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="AA38" s="1" t="s">
+      <c r="AA38" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="2">
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="11"/>
+      <c r="AD38" s="10">
         <v>75</v>
       </c>
-      <c r="AE38" s="2"/>
+      <c r="AE38" s="10"/>
     </row>
     <row r="39" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F39">
+      <c r="F39" s="6">
         <v>25</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I39" s="1" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39">
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="6">
         <v>50</v>
       </c>
-      <c r="M39" s="2">
-        <v>2</v>
-      </c>
-      <c r="O39">
+      <c r="M39" s="7">
+        <v>2</v>
+      </c>
+      <c r="O39" s="9">
         <v>9</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="P39" s="9"/>
+      <c r="Q39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="R39" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="2">
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="10">
         <v>75</v>
       </c>
-      <c r="V39" s="2">
-        <v>3</v>
-      </c>
-      <c r="X39">
+      <c r="V39" s="10">
+        <v>3</v>
+      </c>
+      <c r="X39" s="9">
         <v>9</v>
       </c>
-      <c r="Z39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA39" s="1" t="s">
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA39" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="2">
+      <c r="AB39" s="11"/>
+      <c r="AC39" s="11"/>
+      <c r="AD39" s="10">
         <v>125</v>
       </c>
-      <c r="AE39" s="2"/>
+      <c r="AE39" s="10"/>
     </row>
     <row r="40" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="M40" s="2">
-        <v>2</v>
-      </c>
-      <c r="O40">
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="7">
+        <v>2</v>
+      </c>
+      <c r="O40" s="9">
         <v>10</v>
       </c>
-      <c r="Q40" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1" t="s">
+      <c r="P40" s="9"/>
+      <c r="Q40" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="R40" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="2">
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="10">
         <v>25</v>
       </c>
-      <c r="V40" s="2">
+      <c r="V40" s="10">
         <v>4</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="9">
         <v>10</v>
       </c>
-      <c r="Z40" s="2" t="s">
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AA40" s="1" t="s">
+      <c r="AA40" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-      <c r="AD40" s="2">
+      <c r="AB40" s="11"/>
+      <c r="AC40" s="11"/>
+      <c r="AD40" s="10">
         <v>125</v>
       </c>
-      <c r="AE40" s="2"/>
+      <c r="AE40" s="10"/>
     </row>
     <row r="41" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F41">
+      <c r="F41" s="6">
         <v>26</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="G41" s="6"/>
+      <c r="H41" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41">
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="6">
         <v>150</v>
       </c>
-      <c r="M41" s="2">
-        <v>3</v>
-      </c>
-      <c r="O41">
+      <c r="M41" s="7">
+        <v>3</v>
+      </c>
+      <c r="O41" s="9">
         <v>11</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="P41" s="9"/>
+      <c r="Q41" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="R41" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="2">
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="10">
         <v>25</v>
       </c>
-      <c r="V41" s="2">
-        <v>3</v>
-      </c>
-      <c r="X41">
+      <c r="V41" s="10">
+        <v>3</v>
+      </c>
+      <c r="X41" s="9">
         <v>11</v>
       </c>
-      <c r="Z41" s="2" t="s">
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AA41" s="1" t="s">
+      <c r="AA41" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="2">
+      <c r="AB41" s="11"/>
+      <c r="AC41" s="11"/>
+      <c r="AD41" s="10">
         <v>175</v>
       </c>
-      <c r="AE41" s="2"/>
+      <c r="AE41" s="10"/>
     </row>
     <row r="42" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F42">
+      <c r="F42" s="6">
         <v>27</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="G42" s="6"/>
+      <c r="H42" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42">
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="6">
         <v>150</v>
       </c>
-      <c r="M42" s="2">
-        <v>3</v>
-      </c>
-      <c r="O42">
+      <c r="M42" s="7">
+        <v>3</v>
+      </c>
+      <c r="O42" s="9">
         <v>12</v>
       </c>
-      <c r="Q42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="1" t="s">
+      <c r="P42" s="9"/>
+      <c r="Q42" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="2">
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="10">
         <v>50</v>
       </c>
-      <c r="V42" s="2">
-        <v>3</v>
-      </c>
-      <c r="X42">
+      <c r="V42" s="10">
+        <v>3</v>
+      </c>
+      <c r="X42" s="9">
         <v>12</v>
       </c>
-      <c r="Z42" s="2" t="s">
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AA42" s="1" t="s">
+      <c r="AA42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="2">
+      <c r="AB42" s="11"/>
+      <c r="AC42" s="11"/>
+      <c r="AD42" s="10">
         <v>175</v>
       </c>
-      <c r="AE42" s="2"/>
+      <c r="AE42" s="10"/>
     </row>
     <row r="43" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F43">
+      <c r="F43" s="6">
         <v>28</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="G43" s="6"/>
+      <c r="H43" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43">
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="6">
         <v>150</v>
       </c>
-      <c r="M43" s="2">
-        <v>3</v>
-      </c>
-      <c r="O43">
+      <c r="M43" s="7">
+        <v>3</v>
+      </c>
+      <c r="O43" s="9">
         <v>13</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="P43" s="9"/>
+      <c r="Q43" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="R43" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="2">
+      <c r="S43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="10">
         <v>75</v>
       </c>
-      <c r="V43" s="2">
-        <v>3</v>
-      </c>
-      <c r="X43">
+      <c r="V43" s="10">
+        <v>3</v>
+      </c>
+      <c r="X43" s="6">
         <v>13</v>
       </c>
-      <c r="Z43" s="2" t="s">
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AD43">
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6">
         <v>50</v>
       </c>
-      <c r="AE43" s="2"/>
+      <c r="AE43" s="7"/>
     </row>
     <row r="44" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F44">
+      <c r="F44" s="6">
         <v>29</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="G44" s="6"/>
+      <c r="H44" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44">
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="6">
         <v>150</v>
       </c>
-      <c r="M44" s="2">
-        <v>3</v>
-      </c>
-      <c r="O44">
+      <c r="M44" s="7">
+        <v>3</v>
+      </c>
+      <c r="O44" s="6">
         <v>14</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="P44" s="6"/>
+      <c r="Q44" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="2">
+      <c r="R44" s="8"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="7">
         <v>50</v>
       </c>
-      <c r="V44" s="2">
+      <c r="V44" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="6:31" x14ac:dyDescent="0.25">
-      <c r="F45">
+      <c r="F45" s="6">
         <v>30</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="G45" s="6"/>
+      <c r="H45" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45">
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="6">
         <v>150</v>
       </c>
-      <c r="M45" s="2">
+      <c r="M45" s="7">
         <v>3</v>
       </c>
       <c r="O45">

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3BBDF79-7762-456D-8D3E-9DF5D5D767AB}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE85B6C-4F72-4318-A74D-DB3D686B7333}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="113">
   <si>
     <t>A</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>EE</t>
+  </si>
+  <si>
+    <t>if you palced card iwth n suits, grants vp for set</t>
   </si>
 </sst>
 </file>
@@ -815,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC38A9E3-0959-4F47-9569-6C1D59F951C2}">
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="11.28515625" customWidth="1"/>
@@ -2350,40 +2353,40 @@
       <c r="M31" s="7">
         <v>2</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="6">
         <v>1</v>
       </c>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="R31" s="11" t="s">
+      <c r="P31" s="6"/>
+      <c r="Q31" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="10">
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="7">
         <v>25</v>
       </c>
-      <c r="V31" s="10">
-        <v>3</v>
-      </c>
-      <c r="X31" s="9">
+      <c r="V31" s="7">
+        <v>3</v>
+      </c>
+      <c r="X31" s="6">
         <v>1</v>
       </c>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA31" s="11" t="s">
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="11"/>
-      <c r="AD31" s="10">
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="8"/>
+      <c r="AD31" s="7">
         <v>75</v>
       </c>
-      <c r="AE31" s="10">
+      <c r="AE31" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2398,40 +2401,40 @@
       <c r="M32" s="7">
         <v>2</v>
       </c>
-      <c r="O32" s="9">
-        <v>2</v>
-      </c>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="11" t="s">
+      <c r="O32" s="6">
+        <v>2</v>
+      </c>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="10">
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="7">
         <v>25</v>
       </c>
-      <c r="V32" s="10">
-        <v>3</v>
-      </c>
-      <c r="X32" s="9">
-        <v>2</v>
-      </c>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="11" t="s">
+      <c r="V32" s="7">
+        <v>3</v>
+      </c>
+      <c r="X32" s="6">
+        <v>2</v>
+      </c>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="10">
+      <c r="AB32" s="8"/>
+      <c r="AC32" s="8"/>
+      <c r="AD32" s="7">
         <v>75</v>
       </c>
-      <c r="AE32" s="10">
+      <c r="AE32" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2454,40 +2457,40 @@
       <c r="M33" s="7">
         <v>2</v>
       </c>
-      <c r="O33" s="9">
-        <v>3</v>
-      </c>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="10" t="s">
+      <c r="O33" s="6">
+        <v>3</v>
+      </c>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R33" s="11" t="s">
+      <c r="R33" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="10">
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="7">
         <v>25</v>
       </c>
-      <c r="V33" s="10">
-        <v>3</v>
-      </c>
-      <c r="X33" s="9">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA33" s="11" t="s">
+      <c r="V33" s="7">
+        <v>3</v>
+      </c>
+      <c r="X33" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA33" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="11"/>
-      <c r="AD33" s="9">
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8"/>
+      <c r="AD33" s="6">
         <v>125</v>
       </c>
-      <c r="AE33" s="10">
+      <c r="AE33" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2502,40 +2505,40 @@
       <c r="M34" s="7">
         <v>2</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="6">
         <v>4</v>
       </c>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R34" s="11" t="s">
+      <c r="P34" s="6"/>
+      <c r="Q34" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="10">
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="7">
         <v>25</v>
       </c>
-      <c r="V34" s="10">
-        <v>3</v>
-      </c>
-      <c r="X34" s="9">
+      <c r="V34" s="7">
+        <v>3</v>
+      </c>
+      <c r="X34" s="6">
         <v>4</v>
       </c>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="10" t="s">
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA34" s="11" t="s">
+      <c r="AA34" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="11"/>
-      <c r="AD34" s="10">
+      <c r="AB34" s="8"/>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="7">
         <v>125</v>
       </c>
-      <c r="AE34" s="10">
+      <c r="AE34" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2558,42 +2561,42 @@
       <c r="M35" s="7">
         <v>2</v>
       </c>
-      <c r="O35" s="9">
+      <c r="O35" s="6">
         <v>5</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="P35" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q35" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R35" s="11" t="s">
+      <c r="Q35" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R35" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="10">
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="7">
         <v>25</v>
       </c>
-      <c r="V35" s="10">
-        <v>3</v>
-      </c>
-      <c r="X35" s="9">
+      <c r="V35" s="7">
+        <v>3</v>
+      </c>
+      <c r="X35" s="6">
         <v>5</v>
       </c>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="10" t="s">
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AA35" s="11" t="s">
+      <c r="AA35" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="AB35" s="11"/>
-      <c r="AC35" s="11"/>
-      <c r="AD35" s="10">
+      <c r="AB35" s="8"/>
+      <c r="AC35" s="8"/>
+      <c r="AD35" s="7">
         <v>175</v>
       </c>
-      <c r="AE35" s="10">
+      <c r="AE35" s="7">
         <v>3</v>
       </c>
     </row>
@@ -2608,40 +2611,40 @@
       <c r="M36" s="7">
         <v>2</v>
       </c>
-      <c r="O36" s="9">
+      <c r="O36" s="6">
         <v>6</v>
       </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R36" s="11" t="s">
+      <c r="P36" s="6"/>
+      <c r="Q36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R36" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
-      <c r="U36" s="10">
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="7">
         <v>25</v>
       </c>
-      <c r="V36" s="10">
+      <c r="V36" s="7">
         <v>4</v>
       </c>
-      <c r="X36" s="9">
+      <c r="X36" s="6">
         <v>6</v>
       </c>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="10" t="s">
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AA36" s="11" t="s">
+      <c r="AA36" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="AB36" s="11"/>
-      <c r="AC36" s="11"/>
-      <c r="AD36" s="10">
+      <c r="AB36" s="8"/>
+      <c r="AC36" s="8"/>
+      <c r="AD36" s="7">
         <v>670</v>
       </c>
-      <c r="AE36" s="10">
+      <c r="AE36" s="7">
         <v>3</v>
       </c>
     </row>
@@ -2664,40 +2667,40 @@
       <c r="M37" s="7">
         <v>2</v>
       </c>
-      <c r="O37" s="9">
+      <c r="O37" s="6">
         <v>7</v>
       </c>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R37" s="11" t="s">
+      <c r="P37" s="6"/>
+      <c r="Q37" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R37" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="S37" s="11"/>
-      <c r="T37" s="11"/>
-      <c r="U37" s="10">
+      <c r="S37" s="8"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="7">
         <v>25</v>
       </c>
-      <c r="V37" s="10">
-        <v>3</v>
-      </c>
-      <c r="X37" s="9">
+      <c r="V37" s="7">
+        <v>3</v>
+      </c>
+      <c r="X37" s="6">
         <v>7</v>
       </c>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA37" s="11" t="s">
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA37" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="AB37" s="11"/>
-      <c r="AC37" s="11"/>
-      <c r="AD37" s="10">
+      <c r="AB37" s="8"/>
+      <c r="AC37" s="8"/>
+      <c r="AD37" s="7">
         <v>75</v>
       </c>
-      <c r="AE37" s="10"/>
+      <c r="AE37" s="7"/>
     </row>
     <row r="38" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F38" s="6"/>
@@ -2710,40 +2713,40 @@
       <c r="M38" s="7">
         <v>2</v>
       </c>
-      <c r="O38" s="9">
+      <c r="O38" s="6">
         <v>8</v>
       </c>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R38" s="11" t="s">
+      <c r="P38" s="6"/>
+      <c r="Q38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R38" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="S38" s="11"/>
-      <c r="T38" s="11"/>
-      <c r="U38" s="10">
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="7">
         <v>50</v>
       </c>
-      <c r="V38" s="10">
-        <v>3</v>
-      </c>
-      <c r="X38" s="9">
+      <c r="V38" s="7">
+        <v>3</v>
+      </c>
+      <c r="X38" s="6">
         <v>8</v>
       </c>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="10" t="s">
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AA38" s="11" t="s">
+      <c r="AA38" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="AB38" s="11"/>
-      <c r="AC38" s="11"/>
-      <c r="AD38" s="10">
+      <c r="AB38" s="8"/>
+      <c r="AC38" s="8"/>
+      <c r="AD38" s="7">
         <v>75</v>
       </c>
-      <c r="AE38" s="10"/>
+      <c r="AE38" s="7"/>
     </row>
     <row r="39" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F39" s="6">
@@ -2764,40 +2767,40 @@
       <c r="M39" s="7">
         <v>2</v>
       </c>
-      <c r="O39" s="9">
+      <c r="O39" s="6">
         <v>9</v>
       </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="10" t="s">
+      <c r="P39" s="6"/>
+      <c r="Q39" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="R39" s="11" t="s">
+      <c r="R39" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="S39" s="11"/>
-      <c r="T39" s="11"/>
-      <c r="U39" s="10">
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="7">
         <v>75</v>
       </c>
-      <c r="V39" s="10">
-        <v>3</v>
-      </c>
-      <c r="X39" s="9">
+      <c r="V39" s="7">
+        <v>3</v>
+      </c>
+      <c r="X39" s="6">
         <v>9</v>
       </c>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA39" s="11" t="s">
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA39" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AB39" s="11"/>
-      <c r="AC39" s="11"/>
-      <c r="AD39" s="10">
+      <c r="AB39" s="8"/>
+      <c r="AC39" s="8"/>
+      <c r="AD39" s="7">
         <v>125</v>
       </c>
-      <c r="AE39" s="10"/>
+      <c r="AE39" s="7"/>
     </row>
     <row r="40" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
@@ -2810,40 +2813,40 @@
       <c r="M40" s="7">
         <v>2</v>
       </c>
-      <c r="O40" s="9">
+      <c r="O40" s="6">
         <v>10</v>
       </c>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="R40" s="11" t="s">
+      <c r="P40" s="6"/>
+      <c r="Q40" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R40" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="S40" s="11"/>
-      <c r="T40" s="11"/>
-      <c r="U40" s="10">
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="7">
         <v>25</v>
       </c>
-      <c r="V40" s="10">
+      <c r="V40" s="7">
         <v>4</v>
       </c>
-      <c r="X40" s="9">
+      <c r="X40" s="6">
         <v>10</v>
       </c>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="10" t="s">
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AA40" s="11" t="s">
+      <c r="AA40" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AB40" s="11"/>
-      <c r="AC40" s="11"/>
-      <c r="AD40" s="10">
+      <c r="AB40" s="8"/>
+      <c r="AC40" s="8"/>
+      <c r="AD40" s="7">
         <v>125</v>
       </c>
-      <c r="AE40" s="10"/>
+      <c r="AE40" s="7"/>
     </row>
     <row r="41" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F41" s="6">
@@ -2864,40 +2867,40 @@
       <c r="M41" s="7">
         <v>3</v>
       </c>
-      <c r="O41" s="9">
+      <c r="O41" s="6">
         <v>11</v>
       </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="10" t="s">
+      <c r="P41" s="6"/>
+      <c r="Q41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R41" s="11" t="s">
+      <c r="R41" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="S41" s="11"/>
-      <c r="T41" s="11"/>
-      <c r="U41" s="10">
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="7">
         <v>25</v>
       </c>
-      <c r="V41" s="10">
-        <v>3</v>
-      </c>
-      <c r="X41" s="9">
+      <c r="V41" s="7">
+        <v>3</v>
+      </c>
+      <c r="X41" s="6">
         <v>11</v>
       </c>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="10" t="s">
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AA41" s="11" t="s">
+      <c r="AA41" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="AB41" s="11"/>
-      <c r="AC41" s="11"/>
-      <c r="AD41" s="10">
+      <c r="AB41" s="8"/>
+      <c r="AC41" s="8"/>
+      <c r="AD41" s="7">
         <v>175</v>
       </c>
-      <c r="AE41" s="10"/>
+      <c r="AE41" s="7"/>
     </row>
     <row r="42" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F42" s="6">
@@ -2918,40 +2921,40 @@
       <c r="M42" s="7">
         <v>3</v>
       </c>
-      <c r="O42" s="9">
+      <c r="O42" s="6">
         <v>12</v>
       </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="11" t="s">
+      <c r="P42" s="6"/>
+      <c r="Q42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="S42" s="11"/>
-      <c r="T42" s="11"/>
-      <c r="U42" s="10">
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="7">
         <v>50</v>
       </c>
-      <c r="V42" s="10">
-        <v>3</v>
-      </c>
-      <c r="X42" s="9">
+      <c r="V42" s="7">
+        <v>3</v>
+      </c>
+      <c r="X42" s="6">
         <v>12</v>
       </c>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="10" t="s">
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="AA42" s="11" t="s">
+      <c r="AA42" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="AB42" s="11"/>
-      <c r="AC42" s="11"/>
-      <c r="AD42" s="10">
+      <c r="AB42" s="8"/>
+      <c r="AC42" s="8"/>
+      <c r="AD42" s="7">
         <v>175</v>
       </c>
-      <c r="AE42" s="10"/>
+      <c r="AE42" s="7"/>
     </row>
     <row r="43" spans="6:31" x14ac:dyDescent="0.25">
       <c r="F43" s="6">
@@ -2972,22 +2975,22 @@
       <c r="M43" s="7">
         <v>3</v>
       </c>
-      <c r="O43" s="9">
+      <c r="O43" s="6">
         <v>13</v>
       </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="10" t="s">
+      <c r="P43" s="6"/>
+      <c r="Q43" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="R43" s="11" t="s">
+      <c r="R43" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="S43" s="11"/>
-      <c r="T43" s="11"/>
-      <c r="U43" s="10">
+      <c r="S43" s="8"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="7">
         <v>75</v>
       </c>
-      <c r="V43" s="10">
+      <c r="V43" s="7">
         <v>3</v>
       </c>
       <c r="X43" s="6">
@@ -3095,12 +3098,17 @@
       <c r="T48" s="1"/>
       <c r="V48" s="2"/>
     </row>
-    <row r="49" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:22" x14ac:dyDescent="0.25">
       <c r="Q49" s="2"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="V49" s="2"/>
+    </row>
+    <row r="55" spans="15:22" x14ac:dyDescent="0.25">
+      <c r="O55" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="138">

--- a/GameDisdockIP.xlsx
+++ b/GameDisdockIP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/GMTK 2026 NEW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="447" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BE85B6C-4F72-4318-A74D-DB3D686B7333}"/>
+  <xr:revisionPtr revIDLastSave="451" documentId="8_{047D70A5-312B-42C2-AA54-1E0976B1220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{656DD908-7C3F-4B9C-9A79-3379930EEE06}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11BF88F1-F4C2-45A5-8CCB-3492ED24BECA}"/>
   </bookViews>
@@ -384,7 +384,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,20 +401,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,11 +417,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -446,13 +434,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,13 +454,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -482,10 +462,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+  <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1046,24 +1025,24 @@
       <c r="V8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="X8" s="9">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="9">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="10" t="s">
+      <c r="X8" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AA8" s="11" t="s">
+      <c r="AA8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="10">
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="7">
         <v>150</v>
       </c>
-      <c r="AE8" s="10"/>
+      <c r="AE8" s="7"/>
       <c r="AG8" t="s">
         <v>64</v>
       </c>
@@ -1140,19 +1119,19 @@
       <c r="AE9" s="7">
         <v>2</v>
       </c>
-      <c r="AG9" s="9">
+      <c r="AG9" s="6">
         <v>1</v>
       </c>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="11" t="s">
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="10">
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="7">
         <v>175</v>
       </c>
       <c r="AN9" s="2"/>
@@ -1194,19 +1173,19 @@
       <c r="AE10" s="7">
         <v>2</v>
       </c>
-      <c r="AG10" s="9">
-        <v>2</v>
-      </c>
-      <c r="AH10" s="9"/>
-      <c r="AI10" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="11" t="s">
+      <c r="AG10" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="AK10" s="11"/>
-      <c r="AL10" s="11"/>
-      <c r="AM10" s="10">
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="7">
         <v>175</v>
       </c>
       <c r="AN10" s="2"/>
@@ -1266,19 +1245,19 @@
       <c r="AE11" s="7">
         <v>2</v>
       </c>
-      <c r="AG11" s="9">
-        <v>3</v>
-      </c>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="10" t="s">
+      <c r="AG11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AJ11" s="11" t="s">
+      <c r="AJ11" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AK11" s="11"/>
-      <c r="AL11" s="11"/>
-      <c r="AM11" s="10">
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="7">
         <v>175</v>
       </c>
       <c r="AN11" s="2"/>
@@ -1320,19 +1299,19 @@
       <c r="AE12" s="7">
         <v>2</v>
       </c>
-      <c r="AG12" s="9">
+      <c r="AG12" s="6">
         <v>4</v>
       </c>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ12" s="11" t="s">
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="AK12" s="11"/>
-      <c r="AL12" s="11"/>
-      <c r="AM12" s="10">
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="7">
         <v>175</v>
       </c>
       <c r="AN12" s="2"/>
@@ -1392,19 +1371,19 @@
       <c r="AE13" s="7">
         <v>2</v>
       </c>
-      <c r="AG13" s="9">
+      <c r="AG13" s="6">
         <v>5</v>
       </c>
-      <c r="AH13" s="9"/>
-      <c r="AI13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ13" s="11" t="s">
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ13" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="AK13" s="11"/>
-      <c r="AL13" s="11"/>
-      <c r="AM13" s="10">
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="7">
         <v>175</v>
       </c>
       <c r="AN13" s="2"/>
@@ -1446,19 +1425,19 @@
       <c r="AE14" s="7">
         <v>2</v>
       </c>
-      <c r="AG14" s="9">
+      <c r="AG14" s="6">
         <v>6</v>
       </c>
-      <c r="AH14" s="9"/>
-      <c r="AI14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ14" s="11" t="s">
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ14" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="AK14" s="11"/>
-      <c r="AL14" s="11"/>
-      <c r="AM14" s="10">
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="7">
         <v>275</v>
       </c>
       <c r="AN14" s="2"/>
@@ -1518,19 +1497,19 @@
       <c r="AE15" s="7">
         <v>2</v>
       </c>
-      <c r="AG15" s="9">
+      <c r="AG15" s="6">
         <v>7</v>
       </c>
-      <c r="AH15" s="9"/>
-      <c r="AI15" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ15" s="11" t="s">
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="AK15" s="11"/>
-      <c r="AL15" s="11"/>
-      <c r="AM15" s="10">
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="7">
         <v>275</v>
       </c>
       <c r="AN15" s="2"/>
@@ -1572,19 +1551,19 @@
       <c r="AE16" s="7">
         <v>2</v>
       </c>
-      <c r="AG16" s="9">
+      <c r="AG16" s="6">
         <v>8</v>
       </c>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="10" t="s">
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AJ16" s="11" t="s">
+      <c r="AJ16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="AK16" s="11"/>
-      <c r="AL16" s="11"/>
-      <c r="AM16" s="10">
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="7">
         <v>275</v>
       </c>
       <c r="AN16" s="2"/>
@@ -1644,19 +1623,19 @@
       <c r="AE17" s="7">
         <v>2</v>
       </c>
-      <c r="AG17" s="9">
+      <c r="AG17" s="6">
         <v>9</v>
       </c>
-      <c r="AH17" s="9"/>
-      <c r="AI17" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ17" s="11" t="s">
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ17" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="AK17" s="11"/>
-      <c r="AL17" s="11"/>
-      <c r="AM17" s="10">
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="7">
         <v>275</v>
       </c>
       <c r="AN17" s="2"/>
@@ -1698,19 +1677,19 @@
       <c r="AE18" s="7">
         <v>2</v>
       </c>
-      <c r="AG18" s="9">
+      <c r="AG18" s="6">
         <v>10</v>
       </c>
-      <c r="AH18" s="9"/>
-      <c r="AI18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ18" s="11" t="s">
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AK18" s="11"/>
-      <c r="AL18" s="11"/>
-      <c r="AM18" s="10">
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="7">
         <v>275</v>
       </c>
       <c r="AN18" s="2"/>
@@ -1770,19 +1749,19 @@
       <c r="AE19" s="7">
         <v>3</v>
       </c>
-      <c r="AG19" s="9">
+      <c r="AG19" s="6">
         <v>11</v>
       </c>
-      <c r="AH19" s="9"/>
-      <c r="AI19" s="10" t="s">
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AJ19" s="11" t="s">
+      <c r="AJ19" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="AK19" s="11"/>
-      <c r="AL19" s="11"/>
-      <c r="AM19" s="10">
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="7">
         <v>425</v>
       </c>
       <c r="AN19" s="2"/>
@@ -1842,19 +1821,19 @@
       <c r="AE20" s="7">
         <v>3</v>
       </c>
-      <c r="AG20" s="9">
+      <c r="AG20" s="6">
         <v>12</v>
       </c>
-      <c r="AH20" s="9"/>
-      <c r="AI20" s="10" t="s">
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AJ20" s="11" t="s">
+      <c r="AJ20" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="AK20" s="11"/>
-      <c r="AL20" s="11"/>
-      <c r="AM20" s="10">
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="7">
         <v>425</v>
       </c>
       <c r="AN20" s="2"/>
@@ -1914,19 +1893,19 @@
       <c r="AE21" s="7">
         <v>3</v>
       </c>
-      <c r="AG21" s="9">
+      <c r="AG21" s="6">
         <v>13</v>
       </c>
-      <c r="AH21" s="9"/>
-      <c r="AI21" s="10" t="s">
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AJ21" s="11" t="s">
+      <c r="AJ21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AK21" s="11"/>
-      <c r="AL21" s="11"/>
-      <c r="AM21" s="10">
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="7">
         <v>425</v>
       </c>
       <c r="AN21" s="2"/>
@@ -1986,19 +1965,19 @@
       <c r="AE22" s="7">
         <v>3</v>
       </c>
-      <c r="AG22" s="9">
+      <c r="AG22" s="6">
         <v>14</v>
       </c>
-      <c r="AH22" s="9"/>
-      <c r="AI22" s="10" t="s">
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AJ22" s="11" t="s">
+      <c r="AJ22" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AK22" s="11"/>
-      <c r="AL22" s="11"/>
-      <c r="AM22" s="10">
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="7">
         <v>425</v>
       </c>
       <c r="AN22" s="2"/>
@@ -2058,19 +2037,19 @@
       <c r="AE23" s="7">
         <v>3</v>
       </c>
-      <c r="AG23" s="9">
+      <c r="AG23" s="6">
         <v>15</v>
       </c>
-      <c r="AH23" s="9"/>
-      <c r="AI23" s="10" t="s">
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AJ23" s="11" t="s">
+      <c r="AJ23" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="AK23" s="11"/>
-      <c r="AL23" s="11"/>
-      <c r="AM23" s="10">
+      <c r="AK23" s="8"/>
+      <c r="AL23" s="8"/>
+      <c r="AM23" s="7">
         <v>425</v>
       </c>
       <c r="AN23" s="2"/>
@@ -2126,17 +2105,17 @@
         <v>50</v>
       </c>
       <c r="AE24" s="7"/>
-      <c r="AG24" s="9">
+      <c r="AG24" s="6">
         <v>16</v>
       </c>
-      <c r="AH24" s="9"/>
-      <c r="AI24" s="10" t="s">
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AJ24" s="9"/>
-      <c r="AK24" s="9"/>
-      <c r="AL24" s="9"/>
-      <c r="AM24" s="10">
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="7">
         <v>50</v>
       </c>
       <c r="AN24" s="2"/>
@@ -2642,7 +2621,7 @@
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="7">
-        <v>670</v>
+        <v>2000</v>
       </c>
       <c r="AE36" s="7">
         <v>3</v>
